--- a/docs/ValueSet-genome-build-vs.xlsx
+++ b/docs/ValueSet-genome-build-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T16:34:58+00:00</t>
+    <t>2026-02-20T16:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-genome-build-vs.xlsx
+++ b/docs/ValueSet-genome-build-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T16:31:02+00:00</t>
+    <t>2026-03-05T20:27:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-genome-build-vs.xlsx
+++ b/docs/ValueSet-genome-build-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T20:27:55+00:00</t>
+    <t>2026-03-10T20:40:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-genome-build-vs.xlsx
+++ b/docs/ValueSet-genome-build-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T20:40:46+00:00</t>
+    <t>2026-03-24T15:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-genome-build-vs.xlsx
+++ b/docs/ValueSet-genome-build-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T15:55:50+00:00</t>
+    <t>2026-04-08T14:48:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-genome-build-vs.xlsx
+++ b/docs/ValueSet-genome-build-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:48:38+00:00</t>
+    <t>2026-04-10T13:54:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-genome-build-vs.xlsx
+++ b/docs/ValueSet-genome-build-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T13:54:16+00:00</t>
+    <t>2026-04-21T17:45:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-genome-build-vs.xlsx
+++ b/docs/ValueSet-genome-build-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T17:45:58+00:00</t>
+    <t>2026-06-08T17:19:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-genome-build-vs.xlsx
+++ b/docs/ValueSet-genome-build-vs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T17:19:56+00:00</t>
+    <t>2026-08-05T14:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
